--- a/guitar-chords.xlsx
+++ b/guitar-chords.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Food for thought\experiments\strings-attached\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9097BD53-F2B8-447B-99A9-207D517E7B98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBCDDCB8-2595-4116-8315-A51CBB8B1EE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="282">
   <si>
     <t>Song</t>
   </si>
@@ -1110,15 +1110,41 @@
   <si>
     <t>Enna Sona (OK Jaanu)</t>
   </si>
+  <si>
+    <t>https://youtu.be/E_1_CgZW6fw?si=m0QCQcbApITeGu_i</t>
+  </si>
+  <si>
+    <t>Em7, G, D, Asus</t>
+  </si>
+  <si>
+    <t>Bm7 Fm7 Em</t>
+  </si>
+  <si>
+    <t>Em, A Power Chord, G, A, F# open, B, Bmin11, Bmin7, Dsus2</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1141,13 +1167,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1461,12 +1490,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C139"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="34.4140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.58203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1477,7 +1507,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1485,7 +1515,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1493,7 +1523,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -1501,7 +1531,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -1509,7 +1539,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -1517,7 +1547,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -1525,7 +1555,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -1533,7 +1563,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>277</v>
       </c>
@@ -1541,7 +1571,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -1549,7 +1579,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -1557,7 +1587,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -1565,18 +1595,18 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>24</v>
       </c>
       <c r="B13" t="s">
-        <v>25</v>
+        <v>278</v>
       </c>
       <c r="C13" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>27</v>
       </c>
@@ -1587,15 +1617,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>29</v>
       </c>
       <c r="B15" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -1603,7 +1633,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>32</v>
       </c>
@@ -1611,18 +1641,18 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>34</v>
       </c>
       <c r="B18" t="s">
-        <v>25</v>
+        <v>280</v>
       </c>
       <c r="C18" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>36</v>
       </c>
@@ -1630,7 +1660,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>38</v>
       </c>
@@ -1638,18 +1668,15 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>40</v>
       </c>
-      <c r="B21" t="s">
-        <v>25</v>
-      </c>
-      <c r="C21" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B21" s="1" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>42</v>
       </c>
@@ -1657,7 +1684,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>44</v>
       </c>
@@ -1665,7 +1692,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>46</v>
       </c>
@@ -1673,7 +1700,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>48</v>
       </c>
@@ -1681,7 +1708,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>50</v>
       </c>
@@ -1692,7 +1719,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>53</v>
       </c>
@@ -1700,18 +1727,15 @@
         <v>54</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>55</v>
       </c>
-      <c r="B28" t="s">
-        <v>25</v>
-      </c>
       <c r="C28" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>257</v>
       </c>
@@ -1719,7 +1743,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>58</v>
       </c>
@@ -1727,7 +1751,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>59</v>
       </c>
@@ -1735,7 +1759,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>61</v>
       </c>
@@ -1743,7 +1767,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>62</v>
       </c>
@@ -1751,7 +1775,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>64</v>
       </c>
@@ -1759,7 +1783,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>66</v>
       </c>
@@ -1767,7 +1791,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>68</v>
       </c>
@@ -1775,7 +1799,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>69</v>
       </c>
@@ -1783,7 +1807,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>70</v>
       </c>
@@ -1791,7 +1815,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>71</v>
       </c>
@@ -1799,7 +1823,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>258</v>
       </c>
@@ -1807,7 +1831,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>74</v>
       </c>
@@ -1818,7 +1842,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>76</v>
       </c>
@@ -1826,7 +1850,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>78</v>
       </c>
@@ -1834,7 +1858,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>80</v>
       </c>
@@ -1842,7 +1866,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>82</v>
       </c>
@@ -1853,7 +1877,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>85</v>
       </c>
@@ -1861,7 +1885,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>86</v>
       </c>
@@ -1869,7 +1893,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>87</v>
       </c>
@@ -1877,7 +1901,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>89</v>
       </c>
@@ -1885,7 +1909,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>91</v>
       </c>
@@ -1896,7 +1920,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>92</v>
       </c>
@@ -1904,7 +1928,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>94</v>
       </c>
@@ -1912,7 +1936,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>96</v>
       </c>
@@ -1920,7 +1944,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>98</v>
       </c>
@@ -1931,7 +1955,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>100</v>
       </c>
@@ -1942,7 +1966,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>102</v>
       </c>
@@ -1950,7 +1974,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>104</v>
       </c>
@@ -1958,7 +1982,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>106</v>
       </c>
@@ -1969,7 +1993,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>108</v>
       </c>
@@ -1977,7 +2001,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>110</v>
       </c>
@@ -1985,7 +2009,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>112</v>
       </c>
@@ -1993,7 +2017,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>114</v>
       </c>
@@ -2001,7 +2025,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>116</v>
       </c>
@@ -2009,7 +2033,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>118</v>
       </c>
@@ -2017,7 +2041,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="65" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>120</v>
       </c>
@@ -2025,7 +2049,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="66" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>122</v>
       </c>
@@ -2033,7 +2057,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="67" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>124</v>
       </c>
@@ -2044,7 +2068,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="68" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>127</v>
       </c>
@@ -2052,7 +2076,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="69" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>129</v>
       </c>
@@ -2063,7 +2087,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="70" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>132</v>
       </c>
@@ -2074,7 +2098,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="71" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>135</v>
       </c>
@@ -2082,7 +2106,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="72" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>276</v>
       </c>
@@ -2090,7 +2114,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="73" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>138</v>
       </c>
@@ -2098,7 +2122,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="74" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>140</v>
       </c>
@@ -2109,7 +2133,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="75" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>142</v>
       </c>
@@ -2117,7 +2141,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="76" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>135</v>
       </c>
@@ -2125,7 +2149,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="77" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>145</v>
       </c>
@@ -2136,7 +2160,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="78" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>275</v>
       </c>
@@ -2147,7 +2171,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="79" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>274</v>
       </c>
@@ -2158,7 +2182,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="80" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>150</v>
       </c>
@@ -2166,7 +2190,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="81" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>273</v>
       </c>
@@ -2174,7 +2198,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="82" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>272</v>
       </c>
@@ -2182,7 +2206,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="83" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>154</v>
       </c>
@@ -2193,7 +2217,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="84" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>271</v>
       </c>
@@ -2204,7 +2228,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="85" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>270</v>
       </c>
@@ -2212,7 +2236,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="86" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>159</v>
       </c>
@@ -2223,7 +2247,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="87" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>269</v>
       </c>
@@ -2231,7 +2255,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="88" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>163</v>
       </c>
@@ -2239,7 +2263,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="89" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>165</v>
       </c>
@@ -2250,7 +2274,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="90" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>168</v>
       </c>
@@ -2258,7 +2282,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="91" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>170</v>
       </c>
@@ -2266,7 +2290,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="92" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>172</v>
       </c>
@@ -2274,7 +2298,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="93" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>174</v>
       </c>
@@ -2285,7 +2309,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="94" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>177</v>
       </c>
@@ -2296,7 +2320,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="95" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>180</v>
       </c>
@@ -2304,7 +2328,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="96" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>182</v>
       </c>
@@ -2312,7 +2336,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="97" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>268</v>
       </c>
@@ -2320,7 +2344,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="98" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>267</v>
       </c>
@@ -2328,7 +2352,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="99" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>185</v>
       </c>
@@ -2336,7 +2360,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="100" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>187</v>
       </c>
@@ -2344,7 +2368,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="101" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>189</v>
       </c>
@@ -2352,7 +2376,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="102" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>190</v>
       </c>
@@ -2360,7 +2384,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="103" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>192</v>
       </c>
@@ -2368,7 +2392,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="104" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>194</v>
       </c>
@@ -2376,7 +2400,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="105" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>196</v>
       </c>
@@ -2384,7 +2408,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="106" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>198</v>
       </c>
@@ -2392,7 +2416,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="107" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>200</v>
       </c>
@@ -2400,7 +2424,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="108" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>266</v>
       </c>
@@ -2408,7 +2432,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="109" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>265</v>
       </c>
@@ -2416,7 +2440,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="110" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>204</v>
       </c>
@@ -2424,7 +2448,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="111" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>206</v>
       </c>
@@ -2435,7 +2459,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="112" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>264</v>
       </c>
@@ -2443,7 +2467,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="113" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>210</v>
       </c>
@@ -2451,7 +2475,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="114" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>212</v>
       </c>
@@ -2459,7 +2483,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="115" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>214</v>
       </c>
@@ -2467,7 +2491,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="116" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>263</v>
       </c>
@@ -2475,7 +2499,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="117" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>217</v>
       </c>
@@ -2483,7 +2507,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="118" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>219</v>
       </c>
@@ -2491,7 +2515,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="119" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>262</v>
       </c>
@@ -2499,7 +2523,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="120" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>222</v>
       </c>
@@ -2507,7 +2531,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="121" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>224</v>
       </c>
@@ -2515,7 +2539,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="122" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>226</v>
       </c>
@@ -2523,7 +2547,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="123" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>228</v>
       </c>
@@ -2531,7 +2555,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="124" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>229</v>
       </c>
@@ -2539,7 +2563,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="125" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>231</v>
       </c>
@@ -2547,7 +2571,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="126" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>233</v>
       </c>
@@ -2555,7 +2579,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="127" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>235</v>
       </c>
@@ -2563,7 +2587,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="128" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>237</v>
       </c>
@@ -2571,7 +2595,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="129" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>239</v>
       </c>
@@ -2579,7 +2603,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="130" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>261</v>
       </c>
@@ -2587,7 +2611,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="131" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>242</v>
       </c>
@@ -2595,7 +2619,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="132" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>244</v>
       </c>
@@ -2603,7 +2627,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="133" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>260</v>
       </c>
@@ -2611,7 +2635,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="134" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>247</v>
       </c>
@@ -2619,7 +2643,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="135" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>249</v>
       </c>
@@ -2627,7 +2651,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="136" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>251</v>
       </c>
@@ -2635,7 +2659,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="137" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>253</v>
       </c>
@@ -2643,7 +2667,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="138" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>259</v>
       </c>
@@ -2651,7 +2675,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="139" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>255</v>
       </c>
@@ -2661,8 +2685,9 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:C8 A30:C39 B29:C29 A41:C71 B40:C40 A139:C139 B138:C138 A134:C137 B133:C133 A131:C132 B130:C130 A120:C129 B119:C119 A117:C118 B116:C116 A113:C115 B112:C112 A110:C111 B109:C109 B108:C108 A99:C107 B98:C98 B97:C97 A88:C96 B87:C87 A86:C86 B85:C85 B84:C84 A83:C83 B82:C82 B81:C81 A80:C80 B79:C79 B78:C78 A73:C77 B72:C72 A10:C28 B9:C9" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:C8 A30:C39 B29:C29 A41:C71 B40:C40 A139:C139 B138:C138 A134:C137 B133:C133 A131:C132 B130:C130 A120:C129 B119:C119 A117:C118 B116:C116 A113:C115 B112:C112 A110:C111 B109:C109 B108:C108 A99:C107 B98:C98 B97:C97 A88:C96 B87:C87 A86:C86 B85:C85 B84:C84 A83:C83 B82:C82 B81:C81 A80:C80 B79:C79 B78:C78 A73:C77 B72:C72 A10:C12 B9:C9 A14:C14 A13 C13 A16:C17 A15 C15 A19:C20 A18 C18 A22:C27 A21 A28 C28" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>